--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73048D4E-DC17-7A47-B941-60254B5A4A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{9C846922-A198-6741-A8ED-CC675C7F81B4}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{9C846922-A198-6741-A8ED-CC675C7F81B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73048D4E-DC17-7A47-B941-60254B5A4A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EE72EC-7307-6441-B122-031CB3CE7241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{9C846922-A198-6741-A8ED-CC675C7F81B4}"/>
   </bookViews>
@@ -59,10 +59,6 @@
     <t>嬉しい</t>
   </si>
   <si>
-    <t>ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>YouTubeID</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -161,6 +157,10 @@
   </si>
   <si>
     <t>Joe Hisaishi - Summer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -650,13 +650,13 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -685,10 +685,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4">
         <v>8.701299081220322E-2</v>
@@ -717,10 +717,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="4">
         <v>3.1217461132631477E-2</v>
@@ -749,10 +749,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" s="4">
         <v>1.0324239532424758E-2</v>
@@ -781,10 +781,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4">
         <v>8.5247233081475124E-2</v>
@@ -813,10 +813,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="4">
         <v>4.5133453825328601E-2</v>
@@ -845,10 +845,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4">
         <v>4.0580221556109179E-2</v>
@@ -877,10 +877,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="4">
         <v>0.3296583871845411</v>
@@ -909,10 +909,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="4">
         <v>1.3464532058395127E-2</v>
@@ -941,10 +941,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="4">
         <v>0.1786959022490795</v>
@@ -973,10 +973,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="4">
         <v>0.51779041165342332</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EE72EC-7307-6441-B122-031CB3CE7241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56526A8-5E91-7040-B306-923C496D1451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{9C846922-A198-6741-A8ED-CC675C7F81B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>悲しい</t>
   </si>
@@ -162,6 +162,41 @@
   <si>
     <t>No.</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>keywords</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mistake sport adrenaline life grandson boy video eagle landing vehicle wingsuit diving mountain insanity flight fall style base jump precision ground rocks cliff canyon drone route stunt screen vertigo chance world sleeping bag guide spot week reason experience technology bread bakery vibe depth task bird focus dedication respect spiderman pov tower level school dream blast effort line forest height expression gravity wind glide slope terrain proximity definition racing control batman work falling greeting motorist moment view friend direction power rush partner risk death superpower force pilot gold fort knox regret pleasure ball steel rock fun wish jump mother altitude chute job minute love answer offer skill bravery content safety perception relationship jet feats exercise fear plane existence helmet camera creativity rip distortion kudos gully floor gust priority motorcycle cake fearlessness beauty danger home money amazement day human</t>
+  </si>
+  <si>
+    <t>language nigerian pidgin osas morning place mates birthday username criminal death note friends password cake table test name teacher kids person achievement credits actor movie doctor baby dad food child stroke people mother lunch dinner title africa question paper minecraft enchantment table wifi router back agent 007 respect patience times plot twist burger kid james fear god guy 911 emergency heart attack nobel prize father crowd zipcode opponent battle smith camera skill exam english feeling words parents cameraman water mouth youtube likes google birth certificate signature glass bread world friend newborn keyboard town expression andrew jacked stutter sauce</t>
+  </si>
+  <si>
+    <t>brother son father mother slave life you happiness now creature breeding touch grandparents generation showa burned field food shortage child japan war education society red bull strong person voice way of speaking african water pressure swimsuit safety reaction taste momentum balance acting intentional crime laughter world common tolerance limit dad memories memory black joke escape capture failure reality landmine center of gravity son land papa stunned younger heart fear parent child sea meaning baki hanma reflex core sense of balance abdominal muscles destruction responsibility injury reaction pants year beard human great degree phrasing black and white television luna sea fan past translation african joke nationwide superhero dislocation danger scene terminator john connor motorcycle expression awkward smile safety helmet</t>
+  </si>
+  <si>
+    <t>boss healthbars fake death animations bleed damage catfish river monster loch ness monster shark alligator eel dinosaur prehistoric catfish pokemon namazu amazon florida indonesia spain france thailand russia pripyat river water muddy water algae pool floatie boat bigger boat water chariot fisherman fishing bass fisherman line rod drag lure topwater fight catch release breeder extinction giant animals dam stories spiritual fish psychological fear legs in water thalassophobia courage fear instinct adrenaline jealousy reference illuminati freemason washington lincoln submarine periscope depth guardian deity village monster</t>
+  </si>
+  <si>
+    <t>booby bird blue faced booby chick juvenile adult bird parent bird nest fledging food fish horse mackerel ogasawara okinawa senkaku islands tropical waters nature biology animal bird water surface sea dive flight practice independence adult feathers wings eyes form color scheme plush toy mascot pokemon kyoro chan chums dodo thumbnail youtube recommendation video comments captions photo shooting commemorative photo fisherman fishing fishing rod human kindness good person sense of safety peace healing cute loveliness emotion tears wish growth life coexistence encounter miracle precious culture knowledge learning observation behavior wariness adaptation survival danger trust distance interaction conversation question response gesture movement head shaking balance legs feet sound wind event vinyl doll memory memories family father existence god blessing</t>
+  </si>
+  <si>
+    <t>peasant uprising empire ai human reason customer order head theme person technology video day year face euphonium surroundings title bass copyright performance technique life smile suit breath force lightsaber pitch song star wars original backstage laughter heart breakfast dinner hand talent middle rainbow kakapo brain class back name recorder power me music test teacher sudden recommendation opening music friend joke slide whistle left performer euphonium blue shirt healing exam previous day artist music station appearance men performance effort mario kart lower rank online class talk right hakujitsu posture recommendation duty you myself high rating bass guy masterpiece theory game end darth vader sigh asthma growth brass instrument iguchi iroha chan flute bird terminal sense cluster comment classic abdominal muscles tears war retreat motivation parrot sound clothes expression sandwichman date tomizawa parent quarrel child age</t>
+  </si>
+  <si>
+    <t>meme doctor headache google funeral tips bing internet december 2025 tung tung tung sahur 2019 boss music 2020 funeral music visitors kim coffin people time 2016 days family nostalgia friends youtuber burpster music wikipedia wikihow brain rot woman husband memes quality ricardo dance directed by robert d weide funeral dance allergies web md years masterpiece covid 19 person emotion memory legend life thomas the tank engine diesels tom and jerry karen child funeral companies student teacher classmates lockdown kid oompa loompas cough death skeleton scythe robe world funerals technoblade performance respect ghanaian pallbearers minecraft pet wolf quarantine religion song internet culture tiktok og funk gran man hat video youtube corpse mom make a wish astronomia brainrot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rickroll song youtube staff music anger meme internet people achievement petition anthem rick astley president professor exam key comment grandma link voice obama name views qr code shrek endgame universe articles death waluigi teacher answers tiktok recommended school nostalgia diamonds class france quiz presentation kahoot classmates fact history tutorial soviet union google gemini comments times billion songs genders ads minecraft account minecoins years journal project dark web term camiseta hairline moment god future memes reddit 4chan ad video tab self kinder surprise egg friends funeral privilege life mr astley darude sandstorm robux music video avengers endgame english car uncle wedding vows lyrics rickroll day holiday april billy binges shirt bench pier gold streak music time result opening</t>
+  </si>
+  <si>
+    <t>netflix documentary lionel richie ama song race world stevie wonder bruce springsteen styles nov 25 dec 25 tears singers timestamps 1984 famine tigray ethiopia america steve perry lines vocals touring bob dylan cyndi boyfriend peace event talent passion voice personality quincy jones duet arrangement sequence tape music 80s legends auto tune michael jackson golden age pop collaboration work chorus greed love rip little richard kenny rogers infinity war crossover history masterpiece future earth singer playlist corona entertainment industry cindy hope food drive grocery store trucks food era diversity stage swing choir family christmas new year endgame verse presence group stars documentary pekora nostalgia unity pandemic memory spanish aura humanity soul influence worldwide miracle purpose legend classic song emotion tears</t>
+  </si>
+  <si>
+    <t>summer joe hisaishi composer music piece piano melody tone performance conducting monochrome video black and white video visual expression japan japanese summer japanese sensibility season summer vacation summer memories memory nostalgia longing childhood youth growth life family parent child hometown daily life scenery landscape shade blue sky cumulonimbus clouds veranda electric fan shaved ice pool festival countryside quietness coolness healing comfort warmth emotion tears sense of loss hope positivity time past irreversible summer nonexistent memory imagination universality culture japanese culture world empathy</t>
   </si>
 </sst>
 </file>
@@ -641,14 +676,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE5996D-5265-2C42-A03F-3DB462C4DADC}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:11" ht="18">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -679,8 +714,11 @@
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="18">
+    <row r="2" spans="1:11" ht="18">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -711,8 +749,11 @@
       <c r="J2" s="4">
         <v>0.65259743109152402</v>
       </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" ht="18">
+    <row r="3" spans="1:11" ht="18">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -743,8 +784,11 @@
       <c r="J3" s="4">
         <v>0.93999244077145894</v>
       </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" ht="18">
+    <row r="4" spans="1:11" ht="18">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -775,8 +819,11 @@
       <c r="J4" s="4">
         <v>0.94983003698307777</v>
       </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" ht="24">
+    <row r="5" spans="1:11" ht="24">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -807,8 +854,11 @@
       <c r="J5" s="4">
         <v>0.56981045270249164</v>
       </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" ht="18">
+    <row r="6" spans="1:11" ht="18">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -839,8 +889,11 @@
       <c r="J6" s="4">
         <v>0.85151782883786631</v>
       </c>
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" ht="18">
+    <row r="7" spans="1:11" ht="18">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -871,8 +924,11 @@
       <c r="J7" s="4">
         <v>0.86088041444031604</v>
       </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" ht="18">
+    <row r="8" spans="1:11" ht="18">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -903,8 +959,11 @@
       <c r="J8" s="4">
         <v>0.69887578083122714</v>
       </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="9" spans="1:10" ht="18">
+    <row r="9" spans="1:11" ht="18">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -935,8 +994,11 @@
       <c r="J9" s="4">
         <v>0.83533956890283356</v>
       </c>
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="10" spans="1:10" ht="18">
+    <row r="10" spans="1:11" ht="18">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -967,8 +1029,11 @@
       <c r="J10" s="4">
         <v>0.37781419332662525</v>
       </c>
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="11" spans="1:10" ht="18">
+    <row r="11" spans="1:11" ht="18">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -998,6 +1063,9 @@
       </c>
       <c r="J11" s="4">
         <v>0.7217684526078022</v>
+      </c>
+      <c r="K11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
